--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488044_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488044_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.8438</v>
+        <v>10.3593</v>
       </c>
       <c r="E2" t="n">
-        <v>9.6905</v>
+        <v>9.486800000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1533</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>5.7595</v>
@@ -610,13 +610,13 @@
         <v>2.3787</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2429</v>
+        <v>1.7583</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4868</v>
+        <v>1.2831</v>
       </c>
       <c r="U2" t="n">
-        <v>0.756</v>
+        <v>0.4752</v>
       </c>
       <c r="V2" t="n">
         <v>0.4627</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.793</v>
+        <v>6.1559</v>
       </c>
       <c r="E3" t="n">
-        <v>4.774</v>
+        <v>2.9404</v>
       </c>
       <c r="F3" t="n">
-        <v>3.019</v>
+        <v>3.2156</v>
       </c>
       <c r="G3" t="n">
         <v>1.1049</v>
@@ -688,13 +688,13 @@
         <v>2.5769</v>
       </c>
       <c r="S3" t="n">
-        <v>3.5781</v>
+        <v>1.941</v>
       </c>
       <c r="T3" t="n">
-        <v>3.7114</v>
+        <v>1.8778</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1334</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>0.5331</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.9206</v>
+        <v>5.9601</v>
       </c>
       <c r="E4" t="n">
-        <v>2.26</v>
+        <v>3.0749</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6606</v>
+        <v>2.8852</v>
       </c>
       <c r="G4" t="n">
         <v>2.2224</v>
@@ -766,13 +766,13 @@
         <v>2.3787</v>
       </c>
       <c r="S4" t="n">
-        <v>0.37</v>
+        <v>1.4096</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3158</v>
+        <v>1.1307</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0543</v>
+        <v>0.2789</v>
       </c>
       <c r="V4" t="n">
         <v>0.9405</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7531</v>
+        <v>3.333</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6239</v>
+        <v>0.293</v>
       </c>
       <c r="F5" t="n">
-        <v>3.377</v>
+        <v>3.04</v>
       </c>
       <c r="G5" t="n">
         <v>-0.6984</v>
@@ -844,13 +844,13 @@
         <v>2.3787</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5021</v>
+        <v>1.082</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.121</v>
+        <v>0.7958</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6231</v>
+        <v>0.2861</v>
       </c>
       <c r="V5" t="n">
         <v>2.7512</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3981</v>
+        <v>3.0093</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0181</v>
+        <v>0.5931</v>
       </c>
       <c r="F6" t="n">
         <v>2.4162</v>
@@ -922,10 +922,10 @@
         <v>1.9822</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0221</v>
+        <v>0.5891999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.301</v>
+        <v>0.3103</v>
       </c>
       <c r="U6" t="n">
         <v>0.2789</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.1513</v>
+        <v>0.8904</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2723</v>
+        <v>-0.8482</v>
       </c>
       <c r="F7" t="n">
-        <v>1.879</v>
+        <v>1.7386</v>
       </c>
       <c r="G7" t="n">
         <v>-1.3401</v>
@@ -1000,13 +1000,13 @@
         <v>1.9822</v>
       </c>
       <c r="S7" t="n">
-        <v>2.4319</v>
+        <v>1.171</v>
       </c>
       <c r="T7" t="n">
-        <v>2.7093</v>
+        <v>1.5887</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2773</v>
+        <v>-0.4177</v>
       </c>
       <c r="V7" t="n">
         <v>0.2666</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8209</v>
+        <v>-2.0527</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.438</v>
+        <v>-0.6417</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.383</v>
+        <v>-1.4111</v>
       </c>
       <c r="G11" t="n">
         <v>-0.3286</v>
@@ -1312,13 +1312,13 @@
         <v>0.1982</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3888</v>
+        <v>0.1569</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3671</v>
+        <v>0.1634</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0216</v>
+        <v>-0.0065</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8811</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.3806</v>
+        <v>-2.4544</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5592</v>
+        <v>0.4573</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.9398</v>
+        <v>-2.9118</v>
       </c>
       <c r="G12" t="n">
         <v>-0.8001</v>
@@ -1390,13 +1390,13 @@
         <v>0.5947</v>
       </c>
       <c r="S12" t="n">
-        <v>0.239</v>
+        <v>0.1652</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4919</v>
+        <v>0.3901</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2529</v>
+        <v>-0.2249</v>
       </c>
       <c r="V12" t="n">
         <v>-2.4142</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.6776</v>
+        <v>-2.6766</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.2238</v>
+        <v>-1.307</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4538</v>
+        <v>-1.3696</v>
       </c>
       <c r="G13" t="n">
         <v>-0.1972</v>
@@ -1468,13 +1468,13 @@
         <v>1.3876</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0928</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3744</v>
+        <v>0.5424</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7185</v>
+        <v>-0.6342</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6036</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.6849</v>
+        <v>-5.2285</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.3743</v>
+        <v>-4.1706</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.3106</v>
+        <v>-1.0579</v>
       </c>
       <c r="G14" t="n">
         <v>0.0266</v>
@@ -1546,13 +1546,13 @@
         <v>0.9911</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3417</v>
+        <v>0.1147</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3047</v>
+        <v>0.5085</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6465</v>
+        <v>-0.3938</v>
       </c>
       <c r="V14" t="n">
         <v>-1.2071</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>18.804</v>
+        <v>18.8039</v>
       </c>
       <c r="E15" t="n">
-        <v>11.386</v>
+        <v>11.3861</v>
       </c>
       <c r="F15" t="n">
-        <v>7.4179</v>
+        <v>7.417700000000002</v>
       </c>
       <c r="G15" t="n">
         <v>7.695000000000001</v>
@@ -1624,13 +1624,13 @@
         <v>16.849</v>
       </c>
       <c r="S15" t="n">
-        <v>8.296200000000001</v>
+        <v>8.296100000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>8.5906</v>
+        <v>8.5908</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2947</v>
+        <v>-0.2948</v>
       </c>
       <c r="V15" t="n">
         <v>-1.1519</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.2089</v>
+        <v>3.0041</v>
       </c>
       <c r="E16" t="n">
-        <v>5.7585</v>
+        <v>4.6379</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.5495</v>
+        <v>-1.6338</v>
       </c>
       <c r="G16" t="n">
         <v>1.8148</v>
@@ -1702,13 +1702,13 @@
         <v>1.9822</v>
       </c>
       <c r="S16" t="n">
-        <v>0.634</v>
+        <v>-0.5708</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7916</v>
+        <v>0.671</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.1576</v>
+        <v>-1.2418</v>
       </c>
       <c r="V16" t="n">
         <v>2.7512</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.0098</v>
+        <v>2.8893</v>
       </c>
       <c r="E17" t="n">
-        <v>5.1767</v>
+        <v>4.0562</v>
       </c>
       <c r="F17" t="n">
         <v>-1.1669</v>
@@ -1780,10 +1780,10 @@
         <v>0.7929</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4317</v>
+        <v>0.3111</v>
       </c>
       <c r="T17" t="n">
-        <v>1.663</v>
+        <v>0.5424</v>
       </c>
       <c r="U17" t="n">
         <v>-0.2313</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0723</v>
+        <v>-0.0547</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7254</v>
+        <v>1.8273</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7977</v>
+        <v>-1.882</v>
       </c>
       <c r="G19" t="n">
         <v>1.9096</v>
@@ -1936,13 +1936,13 @@
         <v>1.784</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.526</v>
+        <v>-0.5084</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0072</v>
+        <v>0.0946</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5188</v>
+        <v>-0.603</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2666</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0733</v>
+        <v>-1.9793</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9946</v>
+        <v>-1.5871</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.3922</v>
       </c>
       <c r="G20" t="n">
         <v>-1.2178</v>
@@ -2014,13 +2014,13 @@
         <v>0.7929</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0448</v>
+        <v>-0.9508</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6753</v>
+        <v>-0.2679</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3695</v>
+        <v>-0.6829</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6036</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3374</v>
+        <v>-1.9874</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9948</v>
+        <v>-0.893</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3425</v>
+        <v>-1.0944</v>
       </c>
       <c r="G21" t="n">
         <v>-0.6105</v>
@@ -2092,13 +2092,13 @@
         <v>0.7929</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3127</v>
+        <v>-0.9627</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4368</v>
+        <v>-0.3349</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8759</v>
+        <v>-0.6278</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2071</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. CABRERA SALMON</t>
+          <t>V. CHERNODOLIA SANZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1812</v>
+        <v>-2.8717</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.3111</v>
+        <v>-1.3685</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1299</v>
+        <v>-1.5033</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.1506</v>
+        <v>-3.286</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.4223</v>
+        <v>-0.4966</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2717</v>
+        <v>-2.7894</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.6358</v>
+        <v>-1.4928</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.6358</v>
+        <v>0.5044</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-1.9972</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4852</v>
+        <v>-1.7932</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2136</v>
+        <v>-1.001</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2717</v>
+        <v>-0.7922</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.1982</v>
+        <v>0.1982</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7929</v>
+        <v>1.1893</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0326</v>
+        <v>-0.9911</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3158</v>
+        <v>-0.0917</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3484</v>
+        <v>-0.8994</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.7997</v>
+        <v>1.2071</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.7997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>V. CHERNODOLIA SANZ</t>
+          <t>T. YOME</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.3915</v>
+        <v>-3.3385</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.776</v>
+        <v>-0.6562</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6156</v>
+        <v>-2.6824</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.286</v>
+        <v>-0.1579</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4966</v>
+        <v>-0.0488</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.7894</v>
+        <v>-0.1091</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.4928</v>
+        <v>1.3558</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5044</v>
+        <v>0.6728</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.9972</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.7932</v>
+        <v>-1.5137</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.001</v>
+        <v>-0.7215</v>
       </c>
       <c r="O23" t="n">
         <v>-0.7922</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1982</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1893</v>
+        <v>0.9911</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5109</v>
+        <v>-1.249</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4992</v>
+        <v>-0.2963</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0117</v>
+        <v>-0.9527</v>
       </c>
       <c r="V23" t="n">
-        <v>1.2071</v>
+        <v>-0.9405</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2071</v>
+        <v>0.2666</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>T. YOME</t>
+          <t>S. CABRERA SALMON</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.4286</v>
+        <v>-3.3569</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.5543</v>
+        <v>-3.5149</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.8743</v>
+        <v>0.158</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1579</v>
+        <v>-2.1506</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.0488</v>
+        <v>-2.4223</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1091</v>
+        <v>0.2717</v>
       </c>
       <c r="J24" t="n">
-        <v>1.3558</v>
+        <v>-2.6358</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6728</v>
+        <v>-2.6358</v>
       </c>
       <c r="L24" t="n">
-        <v>0.6830000000000001</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.5137</v>
+        <v>0.4852</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.7215</v>
+        <v>0.2136</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.7922</v>
+        <v>0.2717</v>
       </c>
       <c r="P24" t="n">
+        <v>-0.1982</v>
+      </c>
+      <c r="Q24" t="n">
         <v>-0.9911</v>
       </c>
-      <c r="Q24" t="n">
-        <v>-1.9822</v>
-      </c>
       <c r="R24" t="n">
-        <v>0.9911</v>
+        <v>0.7929</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3391</v>
+        <v>-0.2083</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1944</v>
+        <v>0.112</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.1447</v>
+        <v>-0.3203</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.9405</v>
+        <v>-0.7997</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2071</v>
+        <v>-0.7997</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.4979</v>
+        <v>-4.5262</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.275</v>
+        <v>-4.6638</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.2229</v>
+        <v>0.1376</v>
       </c>
       <c r="G25" t="n">
         <v>-2.3798</v>
@@ -2404,13 +2404,13 @@
         <v>1.9822</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.1776</v>
+        <v>-1.2059</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7377</v>
+        <v>-0.1265</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.4398</v>
+        <v>-1.0794</v>
       </c>
       <c r="V25" t="n">
         <v>-0.9405</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.3429</v>
+        <v>-6.2061</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.4752</v>
+        <v>-5.5583</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.8678</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="G26" t="n">
         <v>-1.8238</v>
@@ -2482,13 +2482,13 @@
         <v>1.784</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.418</v>
+        <v>-1.2811</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.9249000000000001</v>
+        <v>-0.0081</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.4931</v>
+        <v>-1.273</v>
       </c>
       <c r="V26" t="n">
         <v>0.0704</v>
@@ -2515,22 +2515,22 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-18.8037</v>
+        <v>-18.1247</v>
       </c>
       <c r="E27" t="n">
-        <v>-7.417699999999999</v>
+        <v>-7.417700000000003</v>
       </c>
       <c r="F27" t="n">
-        <v>-11.386</v>
+        <v>-10.7071</v>
       </c>
       <c r="G27" t="n">
-        <v>-7.695100000000002</v>
+        <v>-7.6951</v>
       </c>
       <c r="H27" t="n">
         <v>0.3688999999999998</v>
       </c>
       <c r="I27" t="n">
-        <v>-8.0641</v>
+        <v>-8.064100000000002</v>
       </c>
       <c r="J27" t="n">
         <v>2.105</v>
@@ -2545,7 +2545,7 @@
         <v>-9.799999999999999</v>
       </c>
       <c r="N27" t="n">
-        <v>-5.2171</v>
+        <v>-5.217100000000001</v>
       </c>
       <c r="O27" t="n">
         <v>-4.583</v>
@@ -2560,13 +2560,13 @@
         <v>12.8844</v>
       </c>
       <c r="S27" t="n">
-        <v>-8.295999999999999</v>
+        <v>-7.616999999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2948999999999999</v>
+        <v>0.2946</v>
       </c>
       <c r="U27" t="n">
-        <v>-8.590800000000002</v>
+        <v>-7.911599999999999</v>
       </c>
       <c r="V27" t="n">
         <v>1.151799999999999</v>
